--- a/data/trans_dic/P1413-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1413-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,09; 28,72</t>
+          <t>23,18; 28,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,5; 18,34</t>
+          <t>13,49; 18,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 15,69</t>
+          <t>11,11; 15,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,03; 36,12</t>
+          <t>28,06; 35,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,88; 32,02</t>
+          <t>26,9; 32,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,82; 29,64</t>
+          <t>24,43; 29,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,04; 25,52</t>
+          <t>20,02; 25,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,43; 54,18</t>
+          <t>48,91; 54,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,13; 29,75</t>
+          <t>25,9; 29,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,42; 24,01</t>
+          <t>20,46; 24,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,67; 20,69</t>
+          <t>16,83; 20,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,61; 46,16</t>
+          <t>41,18; 45,59</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 13,6</t>
+          <t>10,54; 13,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,03</t>
+          <t>5,64; 8,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 8,1</t>
+          <t>5,89; 8,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,55; 17,47</t>
+          <t>15,36; 18,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,81; 15,31</t>
+          <t>11,96; 15,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,78; 15,24</t>
+          <t>11,68; 15,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,87; 12,87</t>
+          <t>9,94; 12,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,68; 47,36</t>
+          <t>24,03; 27,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,57; 13,9</t>
+          <t>11,59; 13,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 10,92</t>
+          <t>8,84; 10,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 10,0</t>
+          <t>8,13; 10,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,57; 34,85</t>
+          <t>20,04; 22,46</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 14,24</t>
+          <t>8,4; 13,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 7,14</t>
+          <t>2,94; 7,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 9,16</t>
+          <t>4,32; 8,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,63; 15,81</t>
+          <t>10,53; 15,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 13,6</t>
+          <t>7,66; 13,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,26; 14,68</t>
+          <t>8,14; 14,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,72</t>
+          <t>5,17; 9,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,75; 24,24</t>
+          <t>18,98; 24,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 12,56</t>
+          <t>8,92; 12,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,77</t>
+          <t>6,2; 9,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,42</t>
+          <t>5,24; 8,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,35; 19,28</t>
+          <t>15,53; 19,27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,99; 17,44</t>
+          <t>14,99; 17,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 10,1</t>
+          <t>8,08; 10,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 9,25</t>
+          <t>7,3; 9,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,47; 19,18</t>
+          <t>17,22; 19,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 20,49</t>
+          <t>17,81; 20,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,77; 19,56</t>
+          <t>16,85; 19,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,74; 15,19</t>
+          <t>12,86; 15,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,09; 45,38</t>
+          <t>29,29; 31,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,88; 18,67</t>
+          <t>16,78; 18,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,86; 14,55</t>
+          <t>12,88; 14,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,39; 11,91</t>
+          <t>10,35; 11,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,79; 34,1</t>
+          <t>23,84; 25,72</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168494</t>
+          <t>182484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>387639</t>
+          <t>423385</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>556133</t>
+          <t>605869</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>238185; 296320</t>
+          <t>239158; 293612</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>131539; 178781</t>
+          <t>131459; 176255</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83832; 118329</t>
+          <t>83818; 120624</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149182; 185657</t>
+          <t>162036; 203946</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>353518; 421110</t>
+          <t>353738; 421179</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>332010; 396574</t>
+          <t>326785; 393032</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>199354; 253794</t>
+          <t>199087; 255567</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>364729; 408052</t>
+          <t>401730; 445116</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>613174; 698151</t>
+          <t>607867; 695335</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>472309; 555141</t>
+          <t>473223; 555505</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>291516; 361848</t>
+          <t>294366; 361212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>527234; 584877</t>
+          <t>576049; 637771</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345649</t>
+          <t>376094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>703288</t>
+          <t>557216</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1048937</t>
+          <t>933310</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>176466; 230255</t>
+          <t>178568; 233132</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>113481; 157775</t>
+          <t>110846; 158683</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>121807; 168207</t>
+          <t>122244; 169983</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>241270; 399386</t>
+          <t>341981; 415260</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>187482; 243022</t>
+          <t>189840; 244840</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>206736; 267343</t>
+          <t>204970; 265538</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>196305; 255903</t>
+          <t>197664; 257729</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>529448; 1058915</t>
+          <t>521315; 594985</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>379565; 456087</t>
+          <t>380417; 453101</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>329632; 405913</t>
+          <t>328868; 405604</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>332213; 406569</t>
+          <t>330342; 408182</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>839993; 1576113</t>
+          <t>880719; 987361</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83914</t>
+          <t>91426</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>140926</t>
+          <t>159276</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>224840</t>
+          <t>250702</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46423; 78519</t>
+          <t>46345; 75996</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13650; 34379</t>
+          <t>14163; 34669</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24708; 50072</t>
+          <t>23629; 49097</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68632; 102075</t>
+          <t>74839; 109354</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36831; 64787</t>
+          <t>36503; 64917</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37864; 67332</t>
+          <t>37330; 66631</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27932; 53360</t>
+          <t>28413; 52531</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>123777; 160035</t>
+          <t>139367; 179430</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>89823; 129134</t>
+          <t>91664; 130934</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56607; 91806</t>
+          <t>58246; 93116</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58012; 92301</t>
+          <t>57487; 93649</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>200384; 251709</t>
+          <t>224304; 278418</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>598057</t>
+          <t>650004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1231853</t>
+          <t>1139877</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1829910</t>
+          <t>1789881</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>491205; 571470</t>
+          <t>491274; 578124</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275302; 345486</t>
+          <t>276160; 345150</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>246054; 312347</t>
+          <t>246584; 310081</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>464227; 661028</t>
+          <t>605044; 700827</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>602194; 692257</t>
+          <t>601826; 696772</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>595404; 694710</t>
+          <t>598286; 689859</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>450052; 536670</t>
+          <t>454139; 540449</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1061499; 1656049</t>
+          <t>1090834; 1190489</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1123590; 1242838</t>
+          <t>1116665; 1239970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>896319; 1014387</t>
+          <t>898016; 1014078</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>717734; 823117</t>
+          <t>714910; 824563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1616962; 2419496</t>
+          <t>1725807; 1862136</t>
         </is>
       </c>
     </row>
